--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -36,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,12 +68,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -435,10 +444,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -499,27 +508,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>+407</t>
+          <t>+321</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+407</t>
+          <t>+321</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -538,27 +547,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>+445</t>
+          <t>+340</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+445</t>
+          <t>+340</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -582,22 +591,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>+463</t>
+          <t>+363</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+463</t>
+          <t>+363</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -616,27 +625,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>+478</t>
+          <t>+370</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+478</t>
+          <t>+370</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -653,68 +662,68 @@
       <c r="I5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Elly De La Cruz</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>+482</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>17.2%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>+482</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17.2%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Coby Mayo</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>+424</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>19.1%</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>+424</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>19.1%</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>+497</t>
+          <t>+430</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+497</t>
+          <t>+430</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -733,27 +742,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>+571</t>
+          <t>+432</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>+571</t>
+          <t>+432</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -772,27 +781,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Eugenio Suarez</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+434</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+434</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -809,68 +818,68 @@
       <c r="I9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Tommy Edman</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>+585</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>+585</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Christian Encarnacion-Strand</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>+445</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>+445</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>18.3%</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+451</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+451</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -889,27 +898,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Vladimir Guerrero Jr.</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+464</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+464</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -926,68 +935,68 @@
       <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Freddie Freeman</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>+630</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>+630</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Enrique Hernandez</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>+469</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>+469</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Matt McLain</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1006,27 +1015,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Josue De Paula</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+487</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1045,27 +1054,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+499</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+499</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1084,27 +1093,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+508</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+508</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1123,27 +1132,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+536</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+536</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1162,27 +1171,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+538</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+538</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1197,6 +1206,1410 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Gunnar Henderson</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>+560</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>+560</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Tyler Stephenson</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>+579</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>+579</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Eugenio Suarez</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>+580</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>+580</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Brett Baty</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>+587</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>+587</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Kyle Tucker</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>+599</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>+599</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Kevin McGonigle</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>JJ Bleday</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Colton Cowser</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Freddie Freeman</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>+620</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>+620</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Jared Young</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>+640</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>+640</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Gleyber Torres</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>+650</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>+650</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Dillon Dingler</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Narvaez</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>+690</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>+690</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Matt McLain</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>+730</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>+730</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Bo Bichette</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>+740</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>+740</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Josue De Paula</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>+740</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>+740</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Carson Benge</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Kirk</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>+770</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>+770</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Heston Kjerstad</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>+810</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>+810</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AJ Ewing</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>+820</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>10.9%</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>+820</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>10.9%</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Dane Myers</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>+820</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>10.9%</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>+820</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>10.9%</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Jackson Holliday</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>+860</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>+860</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Juan Brito</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>+890</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>+890</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Marcus Semien</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Josh Smith</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>+910</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>+910</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Colt Keith</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>+910</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>+910</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Ernie Clement</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>+930</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>+930</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Nathan Lukes</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>+990</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>+990</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Andres Gimenez</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>+1000</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>+1000</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Max Clark</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>+1020</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>8.9%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>+1020</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>8.9%</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Brett Callahan</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>+1040</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>+1040</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Hector Rodriguez</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>+1120</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>+1120</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Zach McKinstry</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>8.1%</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>8.1%</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>John Peck</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Brett Bateman</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -513,22 +513,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>+256</t>
+          <t>+243</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+256</t>
+          <t>+243</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>+266</t>
+          <t>+255</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>+266</t>
+          <t>+255</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -625,27 +625,27 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>+284</t>
+          <t>+274</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>+284</t>
+          <t>+274</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>+294</t>
+          <t>+288</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>+294</t>
+          <t>+288</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -703,27 +703,27 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>+303</t>
+          <t>+292</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>+303</t>
+          <t>+292</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -742,27 +742,27 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>+310</t>
+          <t>+295</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>+310</t>
+          <t>+295</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -781,27 +781,27 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>+328</t>
+          <t>+319</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>+328</t>
+          <t>+319</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -825,22 +825,22 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>+345</t>
+          <t>+346</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>+345</t>
+          <t>+346</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -864,22 +864,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>+349</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>+349</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -898,27 +898,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>+374</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+374</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -935,68 +935,68 @@
       <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Mickey Moniak</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>+377</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>+377</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Kody Clemens</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>+374</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>+374</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>+384</t>
+          <t>+378</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>+384</t>
+          <t>+378</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1132,27 +1132,27 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Michael Conforto</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>+417</t>
+          <t>+396</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>+417</t>
+          <t>+396</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1169,68 +1169,68 @@
       <c r="I18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Luis Campusano</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>+419</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Michael Conforto</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>+417</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>19.3%</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>+419</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>+417</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>19.3%</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>+433</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>+433</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1247,146 +1247,146 @@
       <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Coby Mayo</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>+435</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>18.7%</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>+435</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>18.7%</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Zach Neto</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>+426</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>+426</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Francisco Lindor</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>+436</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>18.7%</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>+436</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>18.7%</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Luis Campusano</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Zach Neto</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>+440</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Christian Encarnacion-Strand</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>+440</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>+441</t>
+          <t>+444</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>+441</t>
+          <t>+444</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1405,27 +1405,27 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ronald Acuna Jr.</t>
+          <t>Max Muncy (LAD)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>+456</t>
+          <t>+445</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>+456</t>
+          <t>+445</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1444,27 +1444,27 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>+458</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>+458</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1483,27 +1483,27 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Ronald Acuna Jr.</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>+461</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>+461</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1522,27 +1522,27 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>+462</t>
+          <t>+458</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>+462</t>
+          <t>+458</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1561,27 +1561,27 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>+464</t>
+          <t>+460</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>+464</t>
+          <t>+460</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1600,27 +1600,27 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>+466</t>
+          <t>+461</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>+466</t>
+          <t>+461</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1639,27 +1639,27 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Will Smith (LAD)</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>+468</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>+468</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1678,12 +1678,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+471</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+471</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>+471</t>
+          <t>+472</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>+471</t>
+          <t>+472</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1754,68 +1754,68 @@
       <c r="I33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Samuel Basallo</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>+474</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>+474</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Michael Busch</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>+477</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>17.3%</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>+477</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>17.3%</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>+474</t>
+          <t>+477</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>+474</t>
+          <t>+477</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Heriberto Hernandez</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+478</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+478</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1912,27 +1912,27 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Heriberto Hernandez</t>
+          <t>Luis Garcia (NYY)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>+478</t>
+          <t>+480</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>+478</t>
+          <t>+480</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Luis Garcia (NYY)</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>+480</t>
+          <t>+483</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>+480</t>
+          <t>+483</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1990,27 +1990,27 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Will Smith (LAD)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>+483</t>
+          <t>+490</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>+483</t>
+          <t>+490</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2027,82 +2027,82 @@
       <c r="I40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Christian Encarnacion-Strand</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>+483</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>17.2%</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>+483</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>17.2%</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Eugenio Suarez</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>+496</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>+496</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>George Springer</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>+493</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>+493</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Enrique Hernandez</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>+496</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>+496</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2144,68 +2144,68 @@
       <c r="I43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Tommy Edman</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>+505</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>16.5%</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>+505</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>16.5%</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Jo Adell</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>+511</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>+511</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+514</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+514</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2222,68 +2222,68 @@
       <c r="I45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Jordan Walker</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>+512</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>+512</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Tommy Edman</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>+522</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>+522</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero Jr.</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+528</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+528</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2302,27 +2302,27 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2339,68 +2339,68 @@
       <c r="I48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Enrique Hernandez</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>+515</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>+515</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ozzie Albies</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>+534</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>+534</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Eugenio Suarez</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>+517</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>+517</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2419,27 +2419,27 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>+521</t>
+          <t>+537</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>+521</t>
+          <t>+537</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2456,68 +2456,68 @@
       <c r="I51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Zac Veen</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>+527</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>15.9%</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>+527</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>15.9%</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Josh Bell</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>+539</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>+539</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>+527</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>+527</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2536,27 +2536,27 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+546</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+546</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2614,27 +2614,27 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2653,27 +2653,27 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2692,27 +2692,27 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2731,27 +2731,27 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Griffin Conine</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>+539</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>+539</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2770,27 +2770,27 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>+549</t>
+          <t>+570</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>+549</t>
+          <t>+570</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2809,27 +2809,27 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>+551</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>+551</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2848,27 +2848,27 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>+552</t>
+          <t>+572</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>+552</t>
+          <t>+572</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2887,27 +2887,27 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -2926,27 +2926,27 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Griffin Conine</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>+561</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>+561</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -2965,27 +2965,27 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+580</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+580</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3004,27 +3004,27 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+581</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+581</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>+579</t>
+          <t>+582</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>+579</t>
+          <t>+582</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -3082,27 +3082,27 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+583</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+583</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3126,22 +3126,22 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+589</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+589</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3160,27 +3160,27 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Nolan Gorman</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>+584</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>+584</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3199,27 +3199,27 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3238,27 +3238,27 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>+588</t>
+          <t>+596</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>+588</t>
+          <t>+596</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3277,27 +3277,27 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Nolan Gorman</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3316,27 +3316,27 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3355,7 +3355,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Freddy Fermin</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3394,27 +3394,27 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3433,27 +3433,27 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3511,27 +3511,27 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3550,27 +3550,27 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3589,27 +3589,27 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3628,27 +3628,27 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3667,27 +3667,27 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>T.J. Rumfield</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3706,27 +3706,27 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3745,27 +3745,27 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3784,27 +3784,27 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3823,27 +3823,27 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -3867,22 +3867,22 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3901,27 +3901,27 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3940,27 +3940,27 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3979,27 +3979,27 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4174,27 +4174,27 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>T.J. Rumfield</t>
+          <t>Ha-Seong Kim</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4213,27 +4213,27 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Heston Kjerstad</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4252,27 +4252,27 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4291,27 +4291,27 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Ha-Seong Kim</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4335,22 +4335,22 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4408,27 +4408,27 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Leonardo Bernal</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4447,27 +4447,27 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>AJ Ewing</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4491,22 +4491,22 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>+770</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>+770</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4525,27 +4525,27 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4603,27 +4603,27 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Leonardo Bernal</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4642,27 +4642,27 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Heston Kjerstad</t>
+          <t>Carlos Narvaez</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4681,27 +4681,27 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4720,27 +4720,27 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4759,27 +4759,27 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>AJ Ewing</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -4798,27 +4798,27 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -4837,27 +4837,27 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -4876,27 +4876,27 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -4915,27 +4915,27 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Christian Moore</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Christian Moore</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -5032,27 +5032,27 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5071,27 +5071,27 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5110,27 +5110,27 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Kyren Paris</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5149,27 +5149,27 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5188,27 +5188,27 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5227,27 +5227,27 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5266,27 +5266,27 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Emmanuel Rodriguez</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5305,27 +5305,27 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5344,27 +5344,27 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>Kyren Paris</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5383,27 +5383,27 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5422,27 +5422,27 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>Brett Harris</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5461,27 +5461,27 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Thomas Saggese</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5500,27 +5500,27 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Graham Pauley</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5539,27 +5539,27 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5578,27 +5578,27 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Emmanuel Rodriguez</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5617,27 +5617,27 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Jordan Lawlar</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5656,27 +5656,27 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5695,27 +5695,27 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Brett Harris</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -5734,27 +5734,27 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -5773,27 +5773,27 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Graham Pauley</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -5812,27 +5812,27 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -5851,27 +5851,27 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Josue De Paula</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -5890,27 +5890,27 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -5929,27 +5929,27 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Ryan Waldschmidt</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -5968,27 +5968,27 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>Jordan Lawlar</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6007,27 +6007,27 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Josue De Paula</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6085,27 +6085,27 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6124,27 +6124,27 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6163,27 +6163,27 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6202,27 +6202,27 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6241,27 +6241,27 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6280,27 +6280,27 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Ryan Waldschmidt</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6319,27 +6319,27 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6358,27 +6358,27 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Walker Jenkins</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6397,27 +6397,27 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6436,27 +6436,27 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -6475,27 +6475,27 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Samad Taylor</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6514,27 +6514,27 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6553,27 +6553,27 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Brett Callahan</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6592,27 +6592,27 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6631,27 +6631,27 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6670,27 +6670,27 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -6709,27 +6709,27 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Samad Taylor</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -6748,27 +6748,27 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Walker Jenkins</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -6787,27 +6787,27 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -6826,27 +6826,27 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1340</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1340</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -6865,27 +6865,27 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1340</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1340</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -6904,27 +6904,27 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1420</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1420</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -6943,27 +6943,27 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>Brett Callahan</t>
+          <t>John Peck</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1440</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1440</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -6982,27 +6982,27 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7021,27 +7021,27 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7060,27 +7060,27 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7099,27 +7099,27 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1560</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1560</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7138,27 +7138,27 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Tyler Heineman</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1760</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1760</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7173,357 +7173,6 @@
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>Brett Bateman</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>+1340</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>+1340</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr"/>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>Geraldo Perdomo</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>+1340</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>+1340</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr"/>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>Nico Hoerner</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>+1380</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>6.8%</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>+1380</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>6.8%</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr"/>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I175" s="3" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>Jung Hoo Lee</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>+1420</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>6.6%</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>+1420</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>6.6%</t>
-        </is>
-      </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr"/>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I176" s="3" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>John Peck</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>+1440</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>6.5%</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>+1440</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>6.5%</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr"/>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I177" s="3" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>Steven Kwan</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>+1520</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>6.2%</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>+1520</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>6.2%</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G178" s="3" t="inlineStr"/>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I178" s="3" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>Xavier Edwards</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>+1520</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>6.2%</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>+1520</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>6.2%</t>
-        </is>
-      </c>
-      <c r="F179" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G179" s="3" t="inlineStr"/>
-      <c r="H179" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I179" s="3" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>Zach McKinstry</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>+1540</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>6.1%</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>+1540</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>6.1%</t>
-        </is>
-      </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G180" s="3" t="inlineStr"/>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Heineman</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>+1760</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>5.4%</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>+1760</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>5.4%</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr"/>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I181" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -552,22 +552,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>+255</t>
+          <t>+248</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>+255</t>
+          <t>+248</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -664,27 +664,27 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Aaron Judge</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>+288</t>
+          <t>+281</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>+288</t>
+          <t>+281</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -703,27 +703,27 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Aaron Judge</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>+292</t>
+          <t>+288</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>+292</t>
+          <t>+288</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>+295</t>
+          <t>+296</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>+295</t>
+          <t>+296</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>+319</t>
+          <t>+309</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>+319</t>
+          <t>+309</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -903,22 +903,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>+367</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+367</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -981,22 +981,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>+378</t>
+          <t>+383</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>+378</t>
+          <t>+383</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1210,27 +1210,27 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>+425</t>
+          <t>+421</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>+425</t>
+          <t>+421</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>+426</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>+426</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1286,185 +1286,185 @@
       <c r="I21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Zach Neto</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>+426</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>+426</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Will Smith (LAD)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>+427</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>+427</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Christian Encarnacion-Strand</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Luis Campusano</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>+442</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>+442</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Christian Encarnacion-Strand</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>+442</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>18.5%</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>+442</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>18.5%</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Munetaka Murakami</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>+444</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>18.4%</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>+444</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>18.4%</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Max Muncy (LAD)</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>+445</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>18.3%</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>+445</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>18.3%</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>+454</t>
+          <t>+444</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>+454</t>
+          <t>+444</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1483,27 +1483,27 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Ronald Acuna Jr.</t>
+          <t>Max Muncy (LAD)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>+456</t>
+          <t>+445</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>+456</t>
+          <t>+445</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1522,27 +1522,27 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>+458</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>+458</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1561,27 +1561,27 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Ronald Acuna Jr.</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>+460</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>+460</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1600,27 +1600,27 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>+461</t>
+          <t>+458</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>+461</t>
+          <t>+458</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1639,27 +1639,27 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+460</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+460</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1678,27 +1678,27 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>+471</t>
+          <t>+461</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>+471</t>
+          <t>+461</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>+472</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>+472</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1756,27 +1756,27 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+471</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+471</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1795,27 +1795,27 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+472</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+472</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1834,7 +1834,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Heriberto Hernandez</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>+478</t>
+          <t>+477</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>+478</t>
+          <t>+477</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1912,27 +1912,27 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Luis Garcia (NYY)</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>+480</t>
+          <t>+477</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>+480</t>
+          <t>+477</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -1951,27 +1951,27 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Heriberto Hernandez</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>+483</t>
+          <t>+478</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>+483</t>
+          <t>+478</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -1990,27 +1990,27 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Will Smith (LAD)</t>
+          <t>Luis Garcia (NYY)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+480</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+480</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2029,27 +2029,27 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Eugenio Suarez</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>+496</t>
+          <t>+483</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>+496</t>
+          <t>+483</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2066,107 +2066,107 @@
       <c r="I41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>George Springer</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>+495</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>+495</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Enrique Hernandez</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>+496</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>16.8%</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>+496</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>16.8%</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Ian Happ</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>+504</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>16.6%</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>+504</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>16.6%</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Eugenio Suarez</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+496</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+496</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2185,27 +2185,27 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+504</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+504</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2222,68 +2222,68 @@
       <c r="I45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Tommy Edman</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>+522</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>+522</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Jo Adell</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>+511</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>+511</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+514</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+514</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2300,68 +2300,68 @@
       <c r="I47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Connor Norby</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>+530</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>15.9%</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>+530</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>15.9%</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Tommy Edman</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>+522</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>+522</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+528</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+528</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2378,68 +2378,68 @@
       <c r="I49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Jose Siri</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>+534</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>+534</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Connor Norby</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>+530</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>+530</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>+537</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>+537</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2458,27 +2458,27 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>+539</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>+539</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2497,27 +2497,27 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>+541</t>
+          <t>+537</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>+541</t>
+          <t>+537</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2536,27 +2536,27 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>+546</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>+546</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>+547</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>+547</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2614,27 +2614,27 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>+554</t>
+          <t>+546</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>+554</t>
+          <t>+546</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2653,27 +2653,27 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Vladimir Guerrero Jr.</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2692,27 +2692,27 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2731,27 +2731,27 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Griffin Conine</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>+561</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>+561</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2770,27 +2770,27 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>+570</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>+570</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2809,27 +2809,27 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>+571</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>+571</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2848,27 +2848,27 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Griffin Conine</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>+572</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>+572</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2887,27 +2887,27 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Joshua Baez</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+564</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+564</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -2926,27 +2926,27 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+565</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+565</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -2965,27 +2965,27 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+569</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+569</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3004,27 +3004,27 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>+581</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>+581</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3043,27 +3043,27 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Freddy Fermin</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+572</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+572</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3082,27 +3082,27 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>+583</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>+583</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3121,27 +3121,27 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>+589</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>+589</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3160,27 +3160,27 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+580</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+580</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3199,27 +3199,27 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+583</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>+595</t>
+          <t>+583</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3238,27 +3238,27 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>+596</t>
+          <t>+589</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>+596</t>
+          <t>+589</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3277,27 +3277,27 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Nolan Gorman</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+589</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+589</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3316,27 +3316,27 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3355,27 +3355,27 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+595</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3394,27 +3394,27 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+596</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+596</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3433,27 +3433,27 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3511,27 +3511,27 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3550,27 +3550,27 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3589,27 +3589,27 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3628,27 +3628,27 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>T.J. Rumfield</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3667,27 +3667,27 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>T.J. Rumfield</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3706,27 +3706,27 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3745,27 +3745,27 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3823,27 +3823,27 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Shay Whitcomb</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3940,7 +3940,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Nolan Gorman</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3979,7 +3979,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4018,7 +4018,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4135,27 +4135,27 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4174,27 +4174,27 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Ha-Seong Kim</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4213,27 +4213,27 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Heston Kjerstad</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4252,27 +4252,27 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Shay Whitcomb</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4291,27 +4291,27 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Ha-Seong Kim</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4330,27 +4330,27 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Heston Kjerstad</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4408,27 +4408,27 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Leonardo Bernal</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4447,27 +4447,27 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>AJ Ewing</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4486,27 +4486,27 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4525,27 +4525,27 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4564,27 +4564,27 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>AJ Ewing</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4603,27 +4603,27 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4642,27 +4642,27 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Carlos Narvaez</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4681,27 +4681,27 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4720,27 +4720,27 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4759,27 +4759,27 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -4798,27 +4798,27 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -4837,27 +4837,27 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -4876,27 +4876,27 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Carlos Narvaez</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -4915,27 +4915,27 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Christian Moore</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5032,27 +5032,27 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5071,27 +5071,27 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5110,27 +5110,27 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Kyren Paris</t>
+          <t>Christian Moore</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5149,27 +5149,27 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5188,27 +5188,27 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Leonardo Bernal</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5227,27 +5227,27 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5266,27 +5266,27 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Emmanuel Rodriguez</t>
+          <t>Kyren Paris</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5305,27 +5305,27 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5344,27 +5344,27 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5383,27 +5383,27 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Scott Bandura</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5422,27 +5422,27 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5461,27 +5461,27 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5500,27 +5500,27 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>Graham Pauley</t>
+          <t>Emmanuel Rodriguez</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5539,27 +5539,27 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5578,27 +5578,27 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5617,27 +5617,27 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Jordan Lawlar</t>
+          <t>Graham Pauley</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5656,27 +5656,27 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Grant McCray</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5695,27 +5695,27 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Brett Harris</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -5734,27 +5734,27 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -5773,27 +5773,27 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Jordan Lawlar</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -5812,27 +5812,27 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>Thomas Saggese</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -5851,27 +5851,27 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -5890,27 +5890,27 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Brett Harris</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -5929,27 +5929,27 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Ryan Waldschmidt</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -5968,27 +5968,27 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6007,27 +6007,27 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Josue De Paula</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6046,27 +6046,27 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6085,27 +6085,27 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6124,27 +6124,27 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6163,27 +6163,27 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6202,27 +6202,27 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Josue De Paula</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6241,27 +6241,27 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6280,27 +6280,27 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6319,27 +6319,27 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6358,27 +6358,27 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>Walker Jenkins</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6397,27 +6397,27 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Ryan Waldschmidt</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6436,27 +6436,27 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -6475,27 +6475,27 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Samad Taylor</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6514,27 +6514,27 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>+1180</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>+1180</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6553,27 +6553,27 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>Brett Callahan</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6592,27 +6592,27 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6631,27 +6631,27 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6670,27 +6670,27 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -6709,27 +6709,27 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Walker Jenkins</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -6748,27 +6748,27 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Samad Taylor</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -6787,27 +6787,27 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -6826,27 +6826,27 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -6865,27 +6865,27 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -6904,27 +6904,27 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>+1420</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>+1420</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -6943,27 +6943,27 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>John Peck</t>
+          <t>Brett Callahan</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>+1440</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>+1440</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -6982,27 +6982,27 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>+1520</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>+1520</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7021,27 +7021,27 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>+1520</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>+1520</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7060,27 +7060,27 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>+1520</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>+1520</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7099,27 +7099,27 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>+1560</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>+1560</t>
+          <t>+1300</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7138,27 +7138,27 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>Tyler Heineman</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>+1760</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>+1760</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7173,6 +7173,357 @@
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Chase Meidroth</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr"/>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>Geraldo Perdomo</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>+1340</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>+1340</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr"/>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Nico Hoerner</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>+1420</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>+1420</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr"/>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>Brett Bateman</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>+1420</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>+1420</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr"/>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>John Peck</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>+1480</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>+1480</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr"/>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>Steven Kwan</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>+1520</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>+1520</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr"/>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Xavier Edwards</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>+1520</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>+1520</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr"/>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>Zach McKinstry</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>+1560</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>+1560</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr"/>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Heineman</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>+1760</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>+1760</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr"/>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I181" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I267"/>
+  <dimension ref="A1:I271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -552,22 +552,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>+279</t>
+          <t>+268</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+279</t>
+          <t>+268</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -586,27 +586,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>+281</t>
+          <t>+273</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+281</t>
+          <t>+273</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -625,12 +625,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>+282</t>
+          <t>+281</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+282</t>
+          <t>+281</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -664,27 +664,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Aaron Judge</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+285</t>
+          <t>+283</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+285</t>
+          <t>+283</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -703,27 +703,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>+295</t>
+          <t>+299</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+295</t>
+          <t>+299</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>+301</t>
+          <t>+302</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>+301</t>
+          <t>+302</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -781,27 +781,27 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>+319</t>
+          <t>+310</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>+319</t>
+          <t>+310</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -818,107 +818,107 @@
       <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Ben Rice</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>+324</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>23.6%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>+324</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23.6%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Fernando Tatis Jr.</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>+319</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>+319</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Juan Soto</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>+330</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Christian Encarnacion-Strand</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>+329</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>23.3%</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>+330</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>+329</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>23.3%</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>+334</t>
+          <t>+330</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+334</t>
+          <t>+330</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -937,27 +937,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>+341</t>
+          <t>+334</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+341</t>
+          <t>+334</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -976,27 +976,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>+350</t>
+          <t>+341</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+350</t>
+          <t>+341</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1013,68 +1013,68 @@
       <c r="I14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Coby Mayo</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Shea Langeliers</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>+350</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>22.2%</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>+350</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>22.2%</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>+356</t>
+          <t>+353</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>+356</t>
+          <t>+353</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1093,27 +1093,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>+359</t>
+          <t>+356</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+359</t>
+          <t>+356</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1132,27 +1132,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>+360</t>
+          <t>+359</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+360</t>
+          <t>+359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>+370</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+370</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1210,27 +1210,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>+375</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+375</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1249,27 +1249,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Luis Garcia (NYY)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>+379</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+379</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1288,27 +1288,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Ronald Acuna Jr.</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>+395</t>
+          <t>+370</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+395</t>
+          <t>+370</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1325,68 +1325,68 @@
       <c r="I22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Christian Encarnacion-Strand</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>+404</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>+404</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Spencer Jones</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>+394</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>+394</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Ronald Acuna Jr.</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>+405</t>
+          <t>+395</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+405</t>
+          <t>+395</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1405,27 +1405,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>+407</t>
+          <t>+397</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+407</t>
+          <t>+397</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1444,27 +1444,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>+414</t>
+          <t>+398</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+414</t>
+          <t>+398</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1483,27 +1483,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>+421</t>
+          <t>+403</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+421</t>
+          <t>+403</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1522,27 +1522,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>+421</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+421</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1561,27 +1561,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Heriberto Hernandez</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>+423</t>
+          <t>+407</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>+423</t>
+          <t>+407</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1600,27 +1600,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Luis Garcia (NYY)</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>+424</t>
+          <t>+421</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>+424</t>
+          <t>+421</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1639,27 +1639,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>+425</t>
+          <t>+421</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+425</t>
+          <t>+421</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1678,27 +1678,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Heriberto Hernandez</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>+428</t>
+          <t>+423</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+428</t>
+          <t>+423</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1717,27 +1717,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Eugenio Suarez</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>+429</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+429</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Eugenio Suarez</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>+439</t>
+          <t>+438</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+439</t>
+          <t>+438</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2029,27 +2029,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>+440</t>
+          <t>+443</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+440</t>
+          <t>+443</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2068,27 +2068,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>+440</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+440</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2107,27 +2107,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>+443</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+443</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2146,27 +2146,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2185,27 +2185,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2222,48 +2222,48 @@
       <c r="I45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Austin Riley</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>+454</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>+454</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Bobby Witt Jr.</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>+459</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>+459</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2300,68 +2300,68 @@
       <c r="I47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Randal Grichuk</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>+459</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>+459</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Canzone</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>+465</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>+465</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>+465</t>
+          <t>+468</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+465</t>
+          <t>+468</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2419,27 +2419,27 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>+468</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+468</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2458,27 +2458,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>+472</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+472</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2536,12 +2536,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Josue De Paula</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>+475</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+475</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Rece Hinds</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>+479</t>
+          <t>+476</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+479</t>
+          <t>+476</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2612,43 +2612,43 @@
       <c r="I55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Spencer Torkelson</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>+479</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>17.3%</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>+479</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>17.3%</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Willson Contreras</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2692,27 +2692,27 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>+486</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>+486</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2731,27 +2731,27 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Roman Anthony</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>+487</t>
+          <t>+484</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+487</t>
+          <t>+484</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2770,12 +2770,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>+488</t>
+          <t>+487</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+488</t>
+          <t>+487</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2887,27 +2887,27 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Josue De Paula</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>+492</t>
+          <t>+495</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+492</t>
+          <t>+495</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>+495</t>
+          <t>+497</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+495</t>
+          <t>+497</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2965,27 +2965,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Roman Anthony</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>+495</t>
+          <t>+498</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+495</t>
+          <t>+498</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3002,131 +3002,131 @@
       <c r="I65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Isaac Paredes</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>+496</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>+496</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Griffin Conine</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>+499</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>+499</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Griffin Conine</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>+499</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>+499</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Jackson Chourio</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>+501</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>16.6%</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>+501</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>16.6%</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Victor Mesa Jr.</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>+501</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>16.6%</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>+501</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>16.6%</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Jordan Walker</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>+508</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>+508</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>+509</t>
+          <t>+511</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+509</t>
+          <t>+511</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3160,27 +3160,27 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3199,27 +3199,27 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>+519</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+519</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3277,27 +3277,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>+522</t>
+          <t>+519</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+522</t>
+          <t>+519</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3355,27 +3355,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>+526</t>
+          <t>+522</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+526</t>
+          <t>+522</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3394,27 +3394,27 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Austin Hays</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>+527</t>
+          <t>+523</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>+527</t>
+          <t>+523</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3433,27 +3433,27 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Lazaro Montes</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+526</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+526</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3470,68 +3470,68 @@
       <c r="I77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Oneil Cruz</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>+530</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>15.9%</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>+530</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>15.9%</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Harper</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>+526</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>+526</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Austin Hays</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>+532</t>
+          <t>+527</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>+532</t>
+          <t>+527</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3550,27 +3550,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>Lazaro Montes</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>+533</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>+533</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3589,27 +3589,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>+536</t>
+          <t>+533</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>+536</t>
+          <t>+533</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Vladimir Guerrero Jr.</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>+541</t>
+          <t>+540</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+541</t>
+          <t>+540</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3706,27 +3706,27 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>+545</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>+545</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -3745,27 +3745,27 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>+549</t>
+          <t>+545</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+549</t>
+          <t>+545</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero Jr.</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>+554</t>
+          <t>+555</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+554</t>
+          <t>+555</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3860,68 +3860,68 @@
       <c r="I87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Jac Caglianone</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>+554</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>15.3%</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>+554</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>15.3%</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Adley Rutschman</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>+556</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>+556</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>+555</t>
+          <t>+559</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>+555</t>
+          <t>+559</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>+559</t>
+          <t>+560</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+559</t>
+          <t>+560</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3979,27 +3979,27 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Gleyber Torres</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>+571</t>
+          <t>+568</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+571</t>
+          <t>+568</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4018,27 +4018,27 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Gleyber Torres</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>+574</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>+574</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>+576</t>
+          <t>+574</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+576</t>
+          <t>+574</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4133,53 +4133,53 @@
       <c r="I94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Michael Busch</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>+579</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Jac Caglianone</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>+578</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>14.7%</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>+579</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>+578</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>14.7%</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+579</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+579</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Rece Hinds</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+582</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+582</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4252,27 +4252,27 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+584</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+584</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>+583</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+583</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4330,27 +4330,27 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+592</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+592</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>+588</t>
+          <t>+593</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+588</t>
+          <t>+593</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4413,22 +4413,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+597</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+597</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4447,27 +4447,27 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Leonardo Bernal</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -4484,48 +4484,48 @@
       <c r="I103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Justin Foscue</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>+610</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>14.1%</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>+610</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>14.1%</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Kody Clemens</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Jeremiah Jackson</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4603,27 +4603,27 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -4720,27 +4720,27 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Leonardo Bernal</t>
+          <t>Tyrone Taylor</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Tyrone Taylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -4835,68 +4835,68 @@
       <c r="I112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>Kody Clemens</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>+630</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>+630</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr"/>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Vinnie Pasquantino</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>+640</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>+640</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Michael Gasper</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -4915,27 +4915,27 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Michael Gasper</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -4954,27 +4954,27 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -4993,27 +4993,27 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Jeremiah Jackson</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5032,27 +5032,27 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5071,27 +5071,27 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -5115,22 +5115,22 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -5149,27 +5149,27 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5188,27 +5188,27 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -5266,27 +5266,27 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -5305,27 +5305,27 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -5344,27 +5344,27 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Jake Rogers</t>
+          <t>Rafael Flores</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -5383,27 +5383,27 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -5422,27 +5422,27 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -5461,27 +5461,27 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -5500,27 +5500,27 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Andres Chaparro</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -5539,27 +5539,27 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -5578,27 +5578,27 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -5617,27 +5617,27 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Rafael Flores</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -5656,27 +5656,27 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -5773,27 +5773,27 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -5812,27 +5812,27 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -5851,27 +5851,27 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Andres Chaparro</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -5890,27 +5890,27 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -5968,27 +5968,27 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6046,27 +6046,27 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Matt McLain</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Matt McLain</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -6241,27 +6241,27 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6280,27 +6280,27 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -6319,27 +6319,27 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Brady House</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -6436,27 +6436,27 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Carlos Narvaez</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Christian Moore</t>
+          <t>Alex Freeland</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -6553,7 +6553,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Moises Ballesteros</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -6631,27 +6631,27 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Christian Moore</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -6670,27 +6670,27 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Moises Ballesteros</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -6709,27 +6709,27 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -6748,27 +6748,27 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Bryan De La Cruz</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -6787,27 +6787,27 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -6826,27 +6826,27 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -6865,27 +6865,27 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Yohel Pozo</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -6904,27 +6904,27 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -6943,27 +6943,27 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -6982,27 +6982,27 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -7021,27 +7021,27 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -7060,27 +7060,27 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -7138,27 +7138,27 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Carlos Jorge</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -7177,27 +7177,27 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Carlos Jorge</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -7216,27 +7216,27 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Alex Freeland</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -7255,27 +7255,27 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -7411,27 +7411,27 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -7450,27 +7450,27 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -7489,27 +7489,27 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -7528,27 +7528,27 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -7567,27 +7567,27 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>AJ Ewing</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -7606,27 +7606,27 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -7645,27 +7645,27 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Matt Shaw</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -7684,27 +7684,27 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>AJ Ewing</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -7723,27 +7723,27 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -7762,27 +7762,27 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -7801,27 +7801,27 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Matt Shaw</t>
+          <t>T.J. Rumfield</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -7840,27 +7840,27 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -7879,27 +7879,27 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>T.J. Rumfield</t>
+          <t>Jose Caballero</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -7918,27 +7918,27 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -7957,27 +7957,27 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -7996,27 +7996,27 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -8035,27 +8035,27 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jordan Lawlar</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -8074,27 +8074,27 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -8113,27 +8113,27 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>John Rave</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -8152,27 +8152,27 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Konnor Griffin</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -8191,27 +8191,27 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -8230,27 +8230,27 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Samad Taylor</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -8269,27 +8269,27 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Konnor Griffin</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -8308,27 +8308,27 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Samad Taylor</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -8347,27 +8347,27 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -8386,27 +8386,27 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -8464,27 +8464,27 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -8503,27 +8503,27 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Jordan Lawlar</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -8542,27 +8542,27 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -8581,27 +8581,27 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -8620,27 +8620,27 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -8659,27 +8659,27 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Ali Sanchez</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -8698,12 +8698,12 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -8737,27 +8737,27 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Will Banfield</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
@@ -8776,27 +8776,27 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Nick Sogard</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -8815,27 +8815,27 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Will Banfield</t>
+          <t>Grant McCray</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -8854,27 +8854,27 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -8893,27 +8893,27 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -8932,27 +8932,27 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Yohandy Morales</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
@@ -8971,27 +8971,27 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Grant McCray</t>
+          <t>Maikel Garcia</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
@@ -9010,27 +9010,27 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Luis Torrens</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -9049,27 +9049,27 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
@@ -9088,27 +9088,27 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Yohandy Morales</t>
+          <t>Emmanuel Rodriguez</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -9283,27 +9283,27 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
@@ -9322,27 +9322,27 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Jose Fermin (STL)</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -9439,27 +9439,27 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -9478,27 +9478,27 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -9517,27 +9517,27 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -9561,22 +9561,22 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -9595,27 +9595,27 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -9634,27 +9634,27 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -9673,27 +9673,27 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Nick Sogard</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
@@ -9712,7 +9712,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Harry Ford</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -9790,27 +9790,27 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
@@ -9829,27 +9829,27 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -9907,27 +9907,27 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Brett Bateman</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>+1180</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>+1180</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -9946,27 +9946,27 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Brett Bateman</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -9985,27 +9985,27 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>John Peck</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -10029,22 +10029,22 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
@@ -10063,27 +10063,27 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
@@ -10102,27 +10102,27 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -10141,27 +10141,27 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -10180,27 +10180,27 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -10219,7 +10219,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -10258,27 +10258,27 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Cody Freeman</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andrew Pinckney</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -10336,27 +10336,27 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -10375,27 +10375,27 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>BJ Murray</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -10414,27 +10414,27 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -10453,27 +10453,27 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>BJ Murray</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>+1360</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>+1360</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
@@ -10492,27 +10492,27 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>John Peck</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>+1400</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>+1400</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>+1440</t>
+          <t>+1340</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>+1440</t>
+          <t>+1340</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
@@ -10570,27 +10570,27 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>+1480</t>
+          <t>+1360</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>+1480</t>
+          <t>+1360</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -10609,27 +10609,27 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>+1480</t>
+          <t>+1380</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>+1480</t>
+          <t>+1380</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -10648,27 +10648,27 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>+1500</t>
+          <t>+1400</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>+1500</t>
+          <t>+1400</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -10687,27 +10687,27 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>+1620</t>
+          <t>+1400</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>+1620</t>
+          <t>+1400</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -10726,27 +10726,27 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>+1640</t>
+          <t>+1460</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>+1640</t>
+          <t>+1460</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -10765,27 +10765,27 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>+1680</t>
+          <t>+1500</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>+1680</t>
+          <t>+1500</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
@@ -10804,27 +10804,27 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>+1760</t>
+          <t>+1620</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>+1760</t>
+          <t>+1620</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -10843,27 +10843,27 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>+4200</t>
+          <t>+1640</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>+4200</t>
+          <t>+1640</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
@@ -10878,6 +10878,162 @@
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Austin Martin</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>+1680</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>+1680</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Nasim Nunez</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>+1800</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>+1800</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Jorbit Vivas</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>+1820</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>+1820</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Chandler Simpson</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>+4000</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>+4000</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -1093,27 +1093,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Munetaka Murakami</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>+356</t>
+          <t>+359</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+356</t>
+          <t>+359</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1132,27 +1132,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>+359</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>+359</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>+360</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>+360</t>
+          <t>+367</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Luis Garcia (NYY)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1249,27 +1249,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Luis Garcia (NYY)</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>+367</t>
+          <t>+370</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>+367</t>
+          <t>+370</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1288,27 +1288,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>+370</t>
+          <t>+394</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+370</t>
+          <t>+394</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Ronald Acuna Jr.</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>+394</t>
+          <t>+395</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+394</t>
+          <t>+395</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1366,27 +1366,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Ronald Acuna Jr.</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>+395</t>
+          <t>+397</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+395</t>
+          <t>+397</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>+397</t>
+          <t>+398</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>+397</t>
+          <t>+398</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1444,27 +1444,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>+398</t>
+          <t>+403</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>+398</t>
+          <t>+403</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1483,27 +1483,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1522,27 +1522,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>+405</t>
+          <t>+407</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>+405</t>
+          <t>+407</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1678,27 +1678,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Heriberto Hernandez</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>+423</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+423</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1717,27 +1717,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Eugenio Suarez</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>+425</t>
+          <t>+429</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+425</t>
+          <t>+429</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1754,92 +1754,92 @@
       <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Eugenio Suarez</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>+429</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>+429</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Luis Campusano</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>+432</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>+432</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Luis Campusano</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>+432</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>+432</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Mickey Moniak</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>+434</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>18.7%</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>+434</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>18.7%</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>+434</t>
+          <t>+436</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+434</t>
+          <t>+436</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1873,27 +1873,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>+436</t>
+          <t>+437</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+436</t>
+          <t>+437</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>+437</t>
+          <t>+438</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+437</t>
+          <t>+438</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1990,27 +1990,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>+438</t>
+          <t>+443</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+438</t>
+          <t>+443</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2029,27 +2029,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>+443</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+443</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2107,27 +2107,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2146,27 +2146,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>+454</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+454</t>
+          <t>+456</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2183,43 +2183,43 @@
       <c r="I44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Freddie Freeman</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>+456</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>+456</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Randal Grichuk</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>+459</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>+459</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2261,43 +2261,43 @@
       <c r="I46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Randal Grichuk</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>+459</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>+459</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Heriberto Hernandez</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>+464</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>+464</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2339,48 +2339,48 @@
       <c r="I48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Christian Walker</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>+468</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Griffin Conine</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>+467</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>17.6%</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>+468</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>+467</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>17.6%</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2419,27 +2419,27 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+468</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+468</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2458,27 +2458,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>+474</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+474</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Josue De Paula</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2573,68 +2573,68 @@
       <c r="I54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Rece Hinds</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>+476</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Josue De Paula</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>+474</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>17.4%</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>+476</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>+474</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>17.4%</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Rece Hinds</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>+480</t>
+          <t>+476</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>+480</t>
+          <t>+476</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2690,68 +2690,68 @@
       <c r="I57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Sal Stewart</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>+481</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Willson Contreras</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>17.2%</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>+481</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>17.2%</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Roman Anthony</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>+484</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+484</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2770,27 +2770,27 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Roman Anthony</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>+487</t>
+          <t>+484</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+487</t>
+          <t>+484</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>+489</t>
+          <t>+487</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+489</t>
+          <t>+487</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2848,27 +2848,27 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+489</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+489</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2887,27 +2887,27 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>+495</t>
+          <t>+490</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+495</t>
+          <t>+490</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>+497</t>
+          <t>+495</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+497</t>
+          <t>+495</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2965,27 +2965,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>+498</t>
+          <t>+497</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+498</t>
+          <t>+497</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3002,43 +3002,43 @@
       <c r="I65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Griffin Conine</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>+499</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Carter Jensen</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>+498</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>+499</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>+498</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3236,48 +3236,48 @@
       <c r="I71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Victor Mesa Jr.</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Corbin Carroll</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>+519</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>16.2%</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>+519</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>16.2%</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3750,22 +3750,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>+545</t>
+          <t>+550</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+545</t>
+          <t>+550</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>+579</t>
+          <t>+578</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+579</t>
+          <t>+578</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+579</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+582</t>
+          <t>+579</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4252,27 +4252,27 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>+584</t>
+          <t>+582</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+584</t>
+          <t>+582</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+584</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+584</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4330,27 +4330,27 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>+592</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+592</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4369,27 +4369,27 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>+593</t>
+          <t>+592</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+593</t>
+          <t>+592</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4445,82 +4445,82 @@
       <c r="I102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Kody Clemens</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Leonardo Bernal</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>+600</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>14.3%</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>+600</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>14.3%</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>Kody Clemens</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>+600</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>+600</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr"/>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Tyrone Taylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Tyrone Taylor</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Michael Gasper</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Michael Gasper</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -4954,27 +4954,27 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+650</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Jeremiah Jackson</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Jeremiah Jackson</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5110,27 +5110,27 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -5188,27 +5188,27 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -5344,27 +5344,27 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Rafael Flores</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Jake Rogers</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Rafael Flores</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Brett Sullivan</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Brett Sullivan</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -5773,27 +5773,27 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -5812,27 +5812,27 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Andres Chaparro</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Andres Chaparro</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Matt McLain</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -6163,27 +6163,27 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Matt McLain</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -6319,27 +6319,27 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Brady House</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Alex Freeland</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Alex Freeland</t>
+          <t>Moises Ballesteros</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -6553,7 +6553,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Christian Moore</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Moises Ballesteros</t>
+          <t>Christian Moore</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>Yohel Pozo</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Bryan De La Cruz</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Thomas Saggese</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Yohel Pozo</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -6982,7 +6982,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Carlos Jorge</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Carlos Jorge</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -7372,27 +7372,27 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -7450,27 +7450,27 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>AJ Ewing</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>AJ Ewing</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -7606,27 +7606,27 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Matt Shaw</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -7645,27 +7645,27 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Matt Shaw</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>T.J. Rumfield</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -7801,27 +7801,27 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>T.J. Rumfield</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jordan Lawlar</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -8035,27 +8035,27 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Jordan Lawlar</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Ali Sanchez</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Konnor Griffin</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -8191,27 +8191,27 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>Konnor Griffin</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -8269,27 +8269,27 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -8347,7 +8347,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -8464,27 +8464,27 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -8503,7 +8503,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -8581,27 +8581,27 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -8620,27 +8620,27 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -8659,7 +8659,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Ali Sanchez</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Grant McCray</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Grant McCray</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -8893,27 +8893,27 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Emmanuel Rodriguez</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Yohandy Morales</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Yohandy Morales</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -9088,27 +9088,27 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Emmanuel Rodriguez</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -9166,7 +9166,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -9283,7 +9283,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -9322,7 +9322,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Jose Fermin (STL)</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Jose Fermin (STL)</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -9439,27 +9439,27 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -9595,7 +9595,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Nick Sogard</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -9712,7 +9712,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -9790,7 +9790,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Nick Sogard</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Brett Bateman</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Brett Bateman</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -9946,7 +9946,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -9985,7 +9985,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Harry Ford</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -10102,27 +10102,27 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>LaMonte Wade Jr.</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -10180,27 +10180,27 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -10219,27 +10219,27 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
@@ -10258,7 +10258,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -10297,27 +10297,27 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Andrew Pinckney</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Andrew Pinckney</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -10414,7 +10414,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -10453,7 +10453,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>BJ Murray</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>BJ Murray</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
@@ -10648,7 +10648,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -10687,7 +10687,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">

--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I256"/>
+  <dimension ref="A1:I267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -513,22 +513,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>+268</t>
+          <t>+276</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+268</t>
+          <t>+276</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -547,27 +547,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>+279</t>
+          <t>+280</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+279</t>
+          <t>+280</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -586,27 +586,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>+285</t>
+          <t>+296</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+285</t>
+          <t>+296</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -623,43 +623,43 @@
       <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Kyle Schwarber</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>+291</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>25.6%</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>+291</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>25.6%</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Riley Greene</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>+298</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>25.1%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>+298</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25.1%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+296</t>
+          <t>+301</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+296</t>
+          <t>+301</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -703,27 +703,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>+298</t>
+          <t>+306</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+298</t>
+          <t>+306</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -740,107 +740,107 @@
       <c r="I7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Oneil Cruz</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>+298</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>25.1%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>+298</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25.1%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Kyle Schwarber</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>24.3%</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>24.3%</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Fernando Tatis Jr.</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>+304</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>24.8%</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>+304</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>24.8%</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Shea Langeliers</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>+315</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>+315</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>+304</t>
+          <t>+317</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+304</t>
+          <t>+317</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -857,68 +857,68 @@
       <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Jac Caglianone</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>+309</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>24.4%</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>+309</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>24.4%</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>James Wood</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>+328</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>+328</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>+315</t>
+          <t>+333</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>+315</t>
+          <t>+333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -935,68 +935,68 @@
       <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Teoscar Hernandez</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Fernando Tatis Jr.</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>+336</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>22.9%</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>+336</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>22.9%</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>+343</t>
+          <t>+338</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+343</t>
+          <t>+338</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1052,68 +1052,68 @@
       <c r="I15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>James Wood</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Jac Caglianone</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>+349</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>22.3%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>+349</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>22.3%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>+349</t>
+          <t>+353</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>+349</t>
+          <t>+353</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1130,43 +1130,43 @@
       <c r="I17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Manny Machado</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Bobby Witt Jr.</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>+354</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>22.0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>+354</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>22.0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1208,48 +1208,48 @@
       <c r="I19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Willson Contreras</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>+359</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>21.8%</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>+359</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>21.8%</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Will Smith (LAD)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>+363</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>+363</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Will Smith (LAD)</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1288,27 +1288,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>+363</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+363</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1327,27 +1327,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>+364</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>+364</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1366,27 +1366,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>+366</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+366</t>
+          <t>+369</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1403,107 +1403,107 @@
       <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Bobby Witt Jr.</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>+371</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>21.2%</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>+371</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>21.2%</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Ben Rice</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>+375</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>+375</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Jake Burger</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>+377</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>+377</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Willson Contreras</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>+390</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>+390</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>+382</t>
+          <t>+392</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+382</t>
+          <t>+392</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1520,131 +1520,131 @@
       <c r="I27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Pete Crow-Armstrong</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>+393</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>+393</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Matt Olson</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Christian Encarnacion-Strand</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>+387</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>20.5%</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>+387</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>20.5%</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Salvador Perez</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>+396</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>+396</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Julio Rodriguez</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>+402</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>+402</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>+402</t>
+          <t>+403</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+402</t>
+          <t>+403</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1678,27 +1678,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1717,27 +1717,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Ronald Acuna Jr.</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>+404</t>
+          <t>+409</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>+404</t>
+          <t>+409</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1754,107 +1754,107 @@
       <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Mookie Betts</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>+409</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>+409</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Salvador Perez</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>+417</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>19.3%</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>+417</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>19.3%</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Pete Crow-Armstrong</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>+415</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>+415</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Basallo</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Ronald Acuna Jr.</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>+421</t>
+          <t>+426</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>+421</t>
+          <t>+426</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1873,27 +1873,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Heriberto Hernandez</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>+422</t>
+          <t>+426</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+422</t>
+          <t>+426</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>+428</t>
+          <t>+430</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+428</t>
+          <t>+430</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1951,27 +1951,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>+430</t>
+          <t>+431</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+430</t>
+          <t>+431</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1990,27 +1990,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Munetaka Murakami</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>+432</t>
+          <t>+435</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+432</t>
+          <t>+435</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2029,27 +2029,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>+433</t>
+          <t>+440</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+433</t>
+          <t>+440</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2068,27 +2068,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>+433</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+433</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2107,27 +2107,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>+439</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+439</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2146,27 +2146,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Griffin Conine</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>+446</t>
+          <t>+442</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+446</t>
+          <t>+442</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2185,27 +2185,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>+446</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+446</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>+449</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+449</t>
+          <t>+450</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2263,27 +2263,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Luis Garcia (NYY)</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2302,27 +2302,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Jahmai Jones</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>+452</t>
+          <t>+455</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+452</t>
+          <t>+455</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>+455</t>
+          <t>+457</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+455</t>
+          <t>+457</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2378,48 +2378,48 @@
       <c r="I49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Bryce Harper</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Luis Garcia (NYY)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>+457</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>18.0%</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>+457</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>18.0%</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Nolan Gorman</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2458,27 +2458,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Nolan Gorman</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>+466</t>
+          <t>+459</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>+466</t>
+          <t>+459</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2495,68 +2495,68 @@
       <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Colson Montgomery</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>+471</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>+471</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Jahmai Jones</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>+466</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>+466</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Abimelec Ortiz</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>+474</t>
+          <t>+469</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+474</t>
+          <t>+469</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+473</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+477</t>
+          <t>+473</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2614,27 +2614,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>+482</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>+482</t>
+          <t>+474</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2653,27 +2653,27 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>+486</t>
+          <t>+476</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+486</t>
+          <t>+476</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2690,68 +2690,68 @@
       <c r="I57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Dillon Dingler</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>+488</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>+488</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Harper</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>+488</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+488</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2770,27 +2770,27 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Brett Callahan</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>+491</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+491</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2809,27 +2809,27 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>+493</t>
+          <t>+482</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+493</t>
+          <t>+482</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2848,27 +2848,27 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Eugenio Suarez</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+482</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+482</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2885,68 +2885,68 @@
       <c r="I62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Enrique Hernandez</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>+494</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>+494</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Jackson Chourio</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>+485</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>+485</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Joshua Baez</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>+498</t>
+          <t>+485</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+498</t>
+          <t>+485</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2965,27 +2965,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>+501</t>
+          <t>+490</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+501</t>
+          <t>+490</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3004,27 +3004,27 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>+501</t>
+          <t>+493</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+501</t>
+          <t>+493</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3048,22 +3048,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>+501</t>
+          <t>+493</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+501</t>
+          <t>+493</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3082,27 +3082,27 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>+503</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+503</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3121,27 +3121,27 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Enrique Hernandez</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>+506</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+506</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3160,27 +3160,27 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>+509</t>
+          <t>+496</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+509</t>
+          <t>+496</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3199,27 +3199,27 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>+510</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+510</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3238,27 +3238,27 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>+510</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+510</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3277,27 +3277,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+503</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+503</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3316,27 +3316,27 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Vladimir Guerrero Jr.</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>+512</t>
+          <t>+504</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+512</t>
+          <t>+504</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3355,27 +3355,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>+513</t>
+          <t>+508</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+513</t>
+          <t>+508</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3392,53 +3392,53 @@
       <c r="I75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Bryan Reynolds</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>+513</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>+513</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Ty France</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>+510</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>+510</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Roman Anthony</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3472,27 +3472,27 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Abimelec Ortiz</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>+516</t>
+          <t>+514</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>+516</t>
+          <t>+514</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3511,27 +3511,27 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Leonardo Bernal</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>+520</t>
+          <t>+516</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>+520</t>
+          <t>+516</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3550,27 +3550,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero Jr.</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>+522</t>
+          <t>+518</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>+522</t>
+          <t>+518</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>+527</t>
+          <t>+528</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+527</t>
+          <t>+528</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>+533</t>
+          <t>+531</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+533</t>
+          <t>+531</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3784,27 +3784,27 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>+536</t>
+          <t>+532</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+536</t>
+          <t>+532</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3823,27 +3823,27 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -3862,27 +3862,27 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Jordan Beck</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>+542</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+542</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -3899,68 +3899,68 @@
       <c r="I88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>Luis Campusano</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>+543</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>15.6%</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>+543</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>15.6%</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Yandy Diaz</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>+538</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>+538</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>+546</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+546</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -3979,27 +3979,27 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Roman Anthony</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>+547</t>
+          <t>+542</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+547</t>
+          <t>+542</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4018,27 +4018,27 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Jordan Beck</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>+548</t>
+          <t>+542</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>+548</t>
+          <t>+542</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4057,27 +4057,27 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>+549</t>
+          <t>+546</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+549</t>
+          <t>+546</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>+551</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+551</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4135,27 +4135,27 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>+553</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>+553</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4174,27 +4174,27 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>+555</t>
+          <t>+548</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+555</t>
+          <t>+548</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4213,27 +4213,27 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>+560</t>
+          <t>+551</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+560</t>
+          <t>+551</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4252,27 +4252,27 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>+564</t>
+          <t>+553</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+564</t>
+          <t>+553</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4289,43 +4289,43 @@
       <c r="I98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Alejandro Kirk</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>+564</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>15.1%</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>+564</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>15.1%</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Luis Campusano</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>+554</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>15.3%</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>+554</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>15.3%</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4335,22 +4335,22 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>+565</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+565</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4369,27 +4369,27 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>+567</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+567</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -4408,27 +4408,27 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>+569</t>
+          <t>+564</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+569</t>
+          <t>+564</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Eugenio Suarez</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>+573</t>
+          <t>+570</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+573</t>
+          <t>+570</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4530,22 +4530,22 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>+574</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>+574</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -4564,27 +4564,27 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>+581</t>
+          <t>+574</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>+581</t>
+          <t>+574</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -4603,27 +4603,27 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>+584</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+584</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -4642,27 +4642,27 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+580</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+580</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -4681,27 +4681,27 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Brett Callahan</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>+593</t>
+          <t>+581</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+593</t>
+          <t>+581</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -4720,27 +4720,27 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>+594</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+594</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -4759,27 +4759,27 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -4798,27 +4798,27 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+593</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+593</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Rafael Flores</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -4991,48 +4991,48 @@
       <c r="I116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>Randal Grichuk</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Adley Rutschman</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>+610</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>+610</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr"/>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Rafael Flores</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5108,68 +5108,68 @@
       <c r="I119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Kody Clemens</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Ezequiel Tovar</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>+610</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>+610</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr"/>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+610</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+620</t>
+          <t>+610</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5186,48 +5186,48 @@
       <c r="I121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Trea Turner</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>+620</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>+620</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Kody Clemens</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>+610</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>14.1%</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>+610</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>14.1%</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr"/>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5266,27 +5266,27 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Leonardo Bernal</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Shay Whitcomb</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Joshua Baez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -5422,27 +5422,27 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -5461,27 +5461,27 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -5500,27 +5500,27 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -5617,27 +5617,27 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>David Fry</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>JJ Bleday</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -5851,27 +5851,27 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Michael Conforto</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -5890,27 +5890,27 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -5929,27 +5929,27 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Michael Conforto</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+660</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -5968,27 +5968,27 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Josue De Paula</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Heston Kjerstad</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6083,68 +6083,68 @@
       <c r="I144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Josue De Paula</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Adael Amador</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>+680</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>12.8%</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>+680</t>
         </is>
       </c>
-      <c r="E145" s="3" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>12.8%</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr"/>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>Moises Ballesteros</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -6241,27 +6241,27 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Shay Whitcomb</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6280,27 +6280,27 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>David Fry</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -6319,27 +6319,27 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Moises Ballesteros</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6358,27 +6358,27 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -6475,27 +6475,27 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Heston Kjerstad</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -6514,27 +6514,27 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -6553,27 +6553,27 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -6592,27 +6592,27 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -6631,27 +6631,27 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -6670,27 +6670,27 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -6709,27 +6709,27 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>+770</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>+770</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -6748,27 +6748,27 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>James McCann</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -6787,27 +6787,27 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Brett Sullivan</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -6826,27 +6826,27 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Brett Sullivan</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -6865,27 +6865,27 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -6904,27 +6904,27 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -6982,27 +6982,27 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -7021,27 +7021,27 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Brett Harris</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -7060,27 +7060,27 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -7099,27 +7099,27 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -7138,27 +7138,27 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -7177,27 +7177,27 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -7216,27 +7216,27 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -7255,27 +7255,27 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Freddy Fermin</t>
+          <t>Nate Eaton</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -7294,27 +7294,27 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -7411,27 +7411,27 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -7450,27 +7450,27 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Konnor Griffin</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -7489,27 +7489,27 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Brett Harris</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -7528,27 +7528,27 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>AJ Ewing</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -7567,27 +7567,27 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Maikel Garcia</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -7606,27 +7606,27 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -7645,27 +7645,27 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -7684,27 +7684,27 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Maikel Garcia</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -7723,27 +7723,27 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -7762,27 +7762,27 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>T.J. Rumfield</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -7801,27 +7801,27 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -7840,27 +7840,27 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -7884,22 +7884,22 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -7918,27 +7918,27 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Agustin Ramirez</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -7957,27 +7957,27 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -7996,27 +7996,27 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -8074,27 +8074,27 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -8113,27 +8113,27 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Christian Moore</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -8152,27 +8152,27 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Ha-Seong Kim</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -8269,27 +8269,27 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>T.J. Rumfield</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -8308,27 +8308,27 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Pedro Pages</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -8347,27 +8347,27 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -8425,27 +8425,27 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
@@ -8464,27 +8464,27 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -8503,27 +8503,27 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Konnor Griffin</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -8542,27 +8542,27 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -8581,27 +8581,27 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -8620,27 +8620,27 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -8659,27 +8659,27 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Luis Torrens</t>
+          <t>Yohandy Morales</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -8698,27 +8698,27 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>AJ Ewing</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -8737,27 +8737,27 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
@@ -8776,27 +8776,27 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -8815,27 +8815,27 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -8854,27 +8854,27 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Yohandy Morales</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -8898,22 +8898,22 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -8932,27 +8932,27 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
@@ -8971,27 +8971,27 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
@@ -9010,27 +9010,27 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -9049,27 +9049,27 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
@@ -9088,27 +9088,27 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -9127,27 +9127,27 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
@@ -9166,27 +9166,27 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -9205,27 +9205,27 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Luis Torrens</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
@@ -9244,27 +9244,27 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Jorge Barrosa</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -9283,27 +9283,27 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Nick Sogard</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
@@ -9322,27 +9322,27 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Christian Moore</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -9361,27 +9361,27 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Ryan Waldschmidt</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
@@ -9400,27 +9400,27 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
@@ -9439,27 +9439,27 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Walker Jenkins</t>
+          <t>Jorge Barrosa</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -9478,27 +9478,27 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>+1100</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -9517,27 +9517,27 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -9556,27 +9556,27 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -9595,27 +9595,27 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Walker Jenkins</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -9634,27 +9634,27 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Ha-Seong Kim</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -9673,27 +9673,27 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Scott Bandura</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
@@ -9712,27 +9712,27 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Adam Frazier</t>
+          <t>Nick Sogard</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -9751,27 +9751,27 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -9790,27 +9790,27 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Austin Hedges</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
@@ -9829,27 +9829,27 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -9868,27 +9868,27 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1060</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -9907,27 +9907,27 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -9946,27 +9946,27 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -9985,27 +9985,27 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Brett Bateman</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1120</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -10024,27 +10024,27 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Jose Fernandez</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
@@ -10063,27 +10063,27 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>+1360</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>+1360</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
@@ -10102,27 +10102,27 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>+1380</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>+1380</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -10141,27 +10141,27 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>+1400</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>+1400</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -10180,27 +10180,27 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Edgar Quero</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>+1460</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>+1460</t>
+          <t>+1160</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -10219,27 +10219,27 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>+1460</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>+1460</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
@@ -10258,27 +10258,27 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>+1500</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>+1500</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -10297,27 +10297,27 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Nick Madrigal</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>+1660</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>+1660</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
@@ -10336,27 +10336,27 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Adam Frazier</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>+2000</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>+2000</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -10375,27 +10375,27 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>+3600</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>+3600</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -10414,27 +10414,27 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>+10000</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>+10000</t>
+          <t>+1280</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -10449,6 +10449,435 @@
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Zach McKinstry</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>+1300</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>+1300</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Brett Bateman</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Austin Hedges</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>+1340</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>+1340</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Wade Meckler</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>+1380</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>+1380</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Nico Hoerner</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Austin Martin</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>+1460</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>+1460</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Xavier Edwards</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>+1480</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>+1480</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Jake Mangum</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>+1580</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>+1580</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Nick Madrigal</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>+1660</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>5.7%</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>+1660</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>5.7%</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Steven Kwan</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>+1940</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>+1940</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Chandler Simpson</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>+3500</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>+3500</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I267"/>
+  <dimension ref="A1:I271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -508,27 +508,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aaron Judge</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>+276</t>
+          <t>+267</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>+276</t>
+          <t>+267</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -547,27 +547,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Aaron Judge</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>+280</t>
+          <t>+276</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>+280</t>
+          <t>+276</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -586,27 +586,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Oneil Cruz</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>+296</t>
+          <t>+280</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+296</t>
+          <t>+280</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -625,27 +625,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>+298</t>
+          <t>+301</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>+298</t>
+          <t>+301</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -664,27 +664,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+301</t>
+          <t>+306</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+301</t>
+          <t>+306</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,107 +701,107 @@
       <c r="I6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Pete Alonso</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>+306</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>+306</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Kyle Schwarber</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>24.3%</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>24.3%</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Kyle Schwarber</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>+311</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>24.3%</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>+311</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>24.3%</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Shea Langeliers</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>+315</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>+315</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>+315</t>
+          <t>+317</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>+315</t>
+          <t>+317</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -820,27 +820,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>James Wood</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>+317</t>
+          <t>+328</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>+317</t>
+          <t>+328</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,27 +859,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>James Wood</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>+328</t>
+          <t>+331</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>+328</t>
+          <t>+331</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1210,27 +1210,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Will Smith (LAD)</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>+363</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>+363</t>
+          <t>+360</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Will Smith (LAD)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1288,27 +1288,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>+369</t>
+          <t>+366</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>+369</t>
+          <t>+366</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1366,27 +1366,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>+369</t>
+          <t>+383</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>+369</t>
+          <t>+383</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1403,107 +1403,107 @@
       <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Ben Rice</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>+375</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>21.1%</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>+375</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>21.1%</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Willson Contreras</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>+390</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>+390</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Willson Contreras</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>+390</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>20.4%</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>+390</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>20.4%</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Pete Crow-Armstrong</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>+393</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>+393</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>+392</t>
+          <t>+394</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>+392</t>
+          <t>+394</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1520,43 +1520,43 @@
       <c r="I27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Pete Crow-Armstrong</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>+393</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>20.3%</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>+393</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>20.3%</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Christian Encarnacion-Strand</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1598,68 +1598,68 @@
       <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Christian Encarnacion-Strand</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>+397</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>+397</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Jordan Walker</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>+403</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>+403</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+405</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1678,27 +1678,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>+405</t>
+          <t>+409</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>+405</t>
+          <t>+409</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1715,185 +1715,185 @@
       <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Mookie Betts</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>+409</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>+409</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Salvador Perez</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>+417</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>19.3%</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>+417</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>19.3%</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Salvador Perez</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>+417</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Spencer Jones</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>+418</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>19.3%</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>+417</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>+418</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>19.3%</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Luis Garcia (NYY)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Samuel Basallo</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>+420</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>+420</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Ronald Acuna Jr.</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>+426</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>+426</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Heriberto Hernandez</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>+426</t>
+          <t>+422</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>+426</t>
+          <t>+422</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1912,27 +1912,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>+430</t>
+          <t>+424</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>+430</t>
+          <t>+424</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Heriberto Hernandez</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Ronald Acuna Jr.</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>+435</t>
+          <t>+434</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>+435</t>
+          <t>+434</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2029,27 +2029,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>+440</t>
+          <t>+435</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>+440</t>
+          <t>+435</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2068,27 +2068,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>+441</t>
+          <t>+436</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+441</t>
+          <t>+436</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>+441</t>
+          <t>+440</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+441</t>
+          <t>+440</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Griffin Conine</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>+442</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+442</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2185,27 +2185,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+441</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2224,27 +2224,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Griffin Conine</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+442</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>+450</t>
+          <t>+442</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>+454</t>
+          <t>+452</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>+454</t>
+          <t>+452</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2302,27 +2302,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>+455</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>+455</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>+457</t>
+          <t>+455</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>+457</t>
+          <t>+455</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Luis Garcia (NYY)</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Nolan Gorman</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>+458</t>
+          <t>+459</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>+458</t>
+          <t>+459</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Nolan Gorman</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2495,68 +2495,68 @@
       <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Jahmai Jones</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>+466</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>17.7%</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>+466</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>17.7%</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Guerrero Jr.</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>+463</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>17.8%</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>+463</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>17.8%</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Abimelec Ortiz</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>+469</t>
+          <t>+466</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>+469</t>
+          <t>+466</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jahmai Jones</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>+473</t>
+          <t>+466</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>+473</t>
+          <t>+466</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2612,68 +2612,68 @@
       <c r="I55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Randy Arozarena</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>+474</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>+474</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Harper</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>+476</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>+476</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2690,68 +2690,68 @@
       <c r="I57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Bryce Harper</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>+480</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Freddie Freeman</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>+482</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>17.2%</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>+480</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>+482</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>17.2%</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>+481</t>
+          <t>+484</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>+481</t>
+          <t>+484</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2770,27 +2770,27 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>+481</t>
+          <t>+488</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>+481</t>
+          <t>+488</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2809,27 +2809,27 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Enrique Hernandez</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>+482</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>+482</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2848,27 +2848,27 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>+482</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>+482</t>
+          <t>+494</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2887,27 +2887,27 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>+485</t>
+          <t>+498</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+485</t>
+          <t>+498</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2926,27 +2926,27 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Joshua Baez</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>+485</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>+485</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2965,27 +2965,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3004,27 +3004,27 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>+493</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+493</t>
+          <t>+502</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3043,27 +3043,27 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>+493</t>
+          <t>+503</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>+493</t>
+          <t>+503</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3082,27 +3082,27 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+503</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+503</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3121,27 +3121,27 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Abimelec Ortiz</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+507</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+507</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3160,27 +3160,27 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>+496</t>
+          <t>+508</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+496</t>
+          <t>+508</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3197,68 +3197,68 @@
       <c r="I70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Jeremy Pena</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>+502</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>16.6%</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>+502</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>16.6%</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Ty France</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>+510</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>+510</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Roman Anthony</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>+502</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+502</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3277,27 +3277,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Leonardo Bernal</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>+503</t>
+          <t>+516</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+503</t>
+          <t>+516</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3316,27 +3316,27 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero Jr.</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>+504</t>
+          <t>+524</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+504</t>
+          <t>+524</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3355,27 +3355,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>+508</t>
+          <t>+527</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+508</t>
+          <t>+527</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3392,68 +3392,68 @@
       <c r="I75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Ty France</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>+510</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>+510</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Gunnar Henderson</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>+528</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>+528</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Roman Anthony</t>
+          <t>Eugenio Suarez</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>+512</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>+512</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3472,27 +3472,27 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>+514</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3511,27 +3511,27 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Leonardo Bernal</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>+516</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>+516</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3550,27 +3550,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>+518</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>+518</t>
+          <t>+530</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3589,27 +3589,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>+524</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>+524</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3628,27 +3628,27 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Joshua Baez</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+528</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -3667,27 +3667,27 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -3706,27 +3706,27 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>+530</t>
+          <t>+536</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>+530</t>
+          <t>+536</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -3745,27 +3745,27 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>+531</t>
+          <t>+537</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+531</t>
+          <t>+537</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -3784,27 +3784,27 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>+532</t>
+          <t>+538</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+532</t>
+          <t>+538</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3823,27 +3823,27 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -3862,27 +3862,27 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>+535</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+535</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -3901,27 +3901,27 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+541</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>+539</t>
+          <t>+542</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>+539</t>
+          <t>+542</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Jordan Beck</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Jordan Beck</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4057,27 +4057,27 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>+546</t>
+          <t>+551</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+546</t>
+          <t>+551</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>+547</t>
+          <t>+553</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+547</t>
+          <t>+553</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4133,68 +4133,68 @@
       <c r="I94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Ryan O'Hearn</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>+547</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>15.5%</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>+547</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>15.5%</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Luis Campusano</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>+554</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>15.3%</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>+554</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>15.3%</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>+548</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>+548</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4213,27 +4213,27 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>+551</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>+551</t>
+          <t>+554</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4252,27 +4252,27 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>+553</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>+553</t>
+          <t>+558</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4289,68 +4289,68 @@
       <c r="I98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Luis Campusano</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>+554</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>15.3%</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>+554</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>15.3%</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr"/>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Canzone</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>+559</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>+559</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+558</t>
+          <t>+561</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>+561</t>
+          <t>+564</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>+561</t>
+          <t>+564</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4408,27 +4408,27 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>+564</t>
+          <t>+566</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>+564</t>
+          <t>+566</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Eugenio Suarez</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>+570</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>+570</t>
+          <t>+571</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4603,27 +4603,27 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+585</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+585</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -4642,27 +4642,27 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+586</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -4681,27 +4681,27 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Brett Callahan</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>+581</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>+581</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -4720,27 +4720,27 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>+586</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -4759,27 +4759,27 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>+590</t>
+          <t>+593</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>+590</t>
+          <t>+593</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -4798,27 +4798,27 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>+593</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>+593</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Brett Callahan</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -4993,27 +4993,27 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Rafael Flores</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Rafael Flores</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5108,43 +5108,43 @@
       <c r="I119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Ezequiel Tovar</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Kody Clemens</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>+610</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>+610</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5154,22 +5154,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5186,43 +5186,43 @@
       <c r="I121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>Kody Clemens</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>+610</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>14.1%</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>+610</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>14.1%</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr"/>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr"/>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>JJ Bleday</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>+620</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>+620</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5305,27 +5305,27 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+620</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -5539,27 +5539,27 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -5578,27 +5578,27 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -5617,27 +5617,27 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -5656,27 +5656,27 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>David Fry</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -5695,27 +5695,27 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+640</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>JJ Bleday</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -5851,27 +5851,27 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -5890,27 +5890,27 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Shay Whitcomb</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+670</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -5929,27 +5929,27 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Michael Conforto</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -5968,27 +5968,27 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Michael Conforto</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Josue De Paula</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6044,68 +6044,68 @@
       <c r="I143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Hao-Yu Lee</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Josue De Paula</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t>+680</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>12.8%</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>+680</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>12.8%</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr"/>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -6124,27 +6124,27 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -6202,27 +6202,27 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Moises Ballesteros</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -6241,27 +6241,27 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Shay Whitcomb</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+720</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6280,27 +6280,27 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Heston Kjerstad</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -6319,27 +6319,27 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6358,27 +6358,27 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Freddy Fermin</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -6397,27 +6397,27 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>+720</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -6436,27 +6436,27 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -6475,27 +6475,27 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Heston Kjerstad</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -6514,27 +6514,27 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -6553,27 +6553,27 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>David Fry</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -6592,27 +6592,27 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Moises Ballesteros</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -6631,27 +6631,27 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Brett Harris</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -6670,27 +6670,27 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>James McCann</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>+740</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -6709,27 +6709,27 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>James McCann</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Brett Sullivan</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Joe Mack</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -6982,7 +6982,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Joe Mack</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Brett Harris</t>
+          <t>Brett Sullivan</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -7216,27 +7216,27 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Nate Eaton</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Nate Eaton</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -7333,27 +7333,27 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -7372,27 +7372,27 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -7411,7 +7411,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Konnor Griffin</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -7528,27 +7528,27 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -7567,27 +7567,27 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -7606,27 +7606,27 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -7645,27 +7645,27 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -7684,27 +7684,27 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Maikel Garcia</t>
+          <t>Tommy Pham</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -7723,27 +7723,27 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -7762,27 +7762,27 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -7801,27 +7801,27 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -7840,27 +7840,27 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Maikel Garcia</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -7879,27 +7879,27 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Gleyber Torres</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -7918,27 +7918,27 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Agustin Ramirez</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -7957,27 +7957,27 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -7996,27 +7996,27 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -8035,27 +8035,27 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>T.J. Rumfield</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -8074,27 +8074,27 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -8113,27 +8113,27 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -8152,27 +8152,27 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Agustin Ramirez</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>+890</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -8191,27 +8191,27 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -8230,27 +8230,27 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Gleyber Torres</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -8269,27 +8269,27 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>T.J. Rumfield</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -8308,27 +8308,27 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Pedro Pages</t>
+          <t>Konnor Griffin</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -8347,27 +8347,27 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -8386,27 +8386,27 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -8425,27 +8425,27 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
@@ -8464,27 +8464,27 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Pedro Pages</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -8503,27 +8503,27 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -8542,27 +8542,27 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -8581,27 +8581,27 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -8620,27 +8620,27 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Brandon Valenzuela</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -8659,27 +8659,27 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Yohandy Morales</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+910</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -8698,27 +8698,27 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>AJ Ewing</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -8737,27 +8737,27 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Yohandy Morales</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
@@ -8776,27 +8776,27 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -8815,27 +8815,27 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>AJ Ewing</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -8854,27 +8854,27 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -8893,27 +8893,27 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -8932,27 +8932,27 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
@@ -8971,27 +8971,27 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
@@ -9010,27 +9010,27 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>+950</t>
+          <t>+940</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -9049,27 +9049,27 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Christian Moore</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
@@ -9088,27 +9088,27 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -9127,27 +9127,27 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
@@ -9166,27 +9166,27 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>+970</t>
+          <t>+960</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Luis Torrens</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+970</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -9244,7 +9244,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -9283,27 +9283,27 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
@@ -9322,27 +9322,27 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Christian Moore</t>
+          <t>Luis Torrens</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>+990</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -9361,27 +9361,27 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Ryan Waldschmidt</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
@@ -9400,27 +9400,27 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
@@ -9439,27 +9439,27 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Jorge Barrosa</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+990</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Scott Bandura</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -9517,27 +9517,27 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Ryan Waldschmidt</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -9556,27 +9556,27 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>+1020</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -9595,27 +9595,27 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Walker Jenkins</t>
+          <t>Jorge Barrosa</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -9634,27 +9634,27 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Ha-Seong Kim</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>+1040</t>
+          <t>+1020</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Scott Bandura</t>
+          <t>Walker Jenkins</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -9712,27 +9712,27 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Nick Sogard</t>
+          <t>Ha-Seong Kim</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -9751,27 +9751,27 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1040</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -9790,7 +9790,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Nick Sogard</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -9868,27 +9868,27 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>+1060</t>
+          <t>+1080</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -9912,22 +9912,22 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -9946,7 +9946,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -9985,27 +9985,27 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Jose Fernandez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Jose Fernandez</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -10102,27 +10102,27 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>+1160</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -10219,7 +10219,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -10258,27 +10258,27 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>+1180</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>+1180</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -10297,27 +10297,27 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>+1240</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
@@ -10336,27 +10336,27 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Adam Frazier</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -10375,27 +10375,27 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1220</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -10414,27 +10414,27 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>+1280</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -10458,22 +10458,22 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
@@ -10492,27 +10492,27 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Brett Bateman</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Austin Hedges</t>
+          <t>Brett Bateman</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>+1340</t>
+          <t>+1240</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
@@ -10570,27 +10570,27 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>+1380</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>+1380</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -10609,27 +10609,27 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>+1440</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>+1440</t>
+          <t>+1260</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -10648,27 +10648,27 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Adam Frazier</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>+1460</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>+1460</t>
+          <t>+1320</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -10687,27 +10687,27 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>+1480</t>
+          <t>+1440</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>+1480</t>
+          <t>+1440</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -10726,27 +10726,27 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>+1580</t>
+          <t>+1460</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>+1580</t>
+          <t>+1460</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -10765,27 +10765,27 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Nick Madrigal</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>+1660</t>
+          <t>+1460</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>+1660</t>
+          <t>+1460</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
@@ -10804,27 +10804,27 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>+1940</t>
+          <t>+1480</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>+1940</t>
+          <t>+1480</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -10843,27 +10843,27 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Nick Madrigal</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>+3500</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>+3500</t>
+          <t>+1520</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
@@ -10878,6 +10878,162 @@
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Jake Mangum</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>+1540</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>6.1%</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>+1540</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>6.1%</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Luisangel Acuna</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>+1620</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>+1620</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Steven Kwan</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>+1940</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>+1940</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Chandler Simpson</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>+4300</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>+4300</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hr_odds.xlsx
+++ b/hr_odds.xlsx
@@ -1025,27 +1025,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>+346</t>
+          <t>+348</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>+353</t>
+          <t>+357</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1072,94 +1072,94 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>+348</t>
+          <t>+351</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+357</t>
+          <t>+353</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+340</t>
+          <t>+350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+350</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>+351</t>
+          <t>+352</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>+353</t>
+          <t>+365</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+350</t>
+          <t>+340</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>+350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1634,94 +1634,94 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Carter Jensen</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>+378</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>20.9%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>+396</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>+370</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>+370</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Jac Caglianone</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>+377</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>+379</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>20.9%</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>+393</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>20.3%</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>+370</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>21.3%</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>+370</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>21.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Carter Jensen</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>+378</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>20.9%</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>+396</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>+370</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>21.3%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>+370</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>21.3%</t>
         </is>
@@ -2245,94 +2245,94 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Canzone</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>+421</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>+444</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>18.4%</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>+410</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>+410</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Bobby Witt Jr.</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>+421</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>+444</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>18.4%</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>+410</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>19.6%</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>+410</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Dominic Canzone</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>+421</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>+444</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>18.4%</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>+410</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>+410</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>19.6%</t>
         </is>
@@ -2388,12 +2388,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>+422</t>
+          <t>+424</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>+438</t>
+          <t>+431</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2423,24 +2423,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>+410</t>
+          <t>+420</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Lazaro Montes</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>+424</t>
+          <t>+425</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>+431</t>
+          <t>+434</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2482,27 +2482,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Lazaro Montes</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>+425</t>
+          <t>+426</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>+434</t>
+          <t>+438</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3091,47 +3091,47 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Kyle Teel</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>+453</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>18.1%</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>+467</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>17.6%</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>+440</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
@@ -3375,178 +3375,178 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>+481</t>
+          <t>+480</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>+479</t>
+          <t>+511</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+470</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>+475</t>
+          <t>+460</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>Bryce Eldridge</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>+481</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>+479</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>17.3%</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>+490</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>+475</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>17.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
           <t>Andrew Benintendi</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>+482</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>17.2%</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>+474</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>17.4%</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>+490</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>16.9%</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Bryan Reynolds</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>+482</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>17.2%</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>+481</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>17.2%</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>+490</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>16.9%</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>+475</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>17.4%</t>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>+485</t>
+          <t>+482</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+481</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+470</t>
+          <t>+490</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3561,47 +3561,47 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Tommy Edman</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>+488</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>17.0%</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>+498</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>+490</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>16.9%</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>+475</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>17.4%</t>
         </is>
@@ -3709,22 +3709,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>+492</t>
+          <t>+500</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+510</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3751,37 +3751,37 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>+504</t>
+          <t>+508</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>+519</t>
+          <t>+496</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>+490</t>
+          <t>+520</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3798,12 +3798,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>+510</t>
+          <t>+511</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>+537</t>
+          <t>+513</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3833,19 +3833,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>+475</t>
+          <t>+500</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>+502</t>
+          <t>+503</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3892,27 +3892,27 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>+511</t>
+          <t>+512</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>+513</t>
+          <t>+516</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3939,17 +3939,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Luis Garcia (NYY)</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>+512</t>
+          <t>+516</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3964,29 +3964,29 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+520</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>+500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Luis Garcia (NYY)</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4001,44 +4001,44 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>+516</t>
+          <t>+529</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+520</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+500</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>+516</t>
+          <t>+518</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4048,44 +4048,44 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>+529</t>
+          <t>+537</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>+520</t>
+          <t>+500</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>+500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>+518</t>
+          <t>+519</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4105,34 +4105,34 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
+          <t>+520</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
           <t>+500</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>16.7%</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Luis Garcia Jr.</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>+519</t>
+          <t>+520</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>+519</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Luis Garcia Jr.</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+521</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4219,61 +4219,61 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Jose Siri</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Yandy Diaz</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>+521</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>+545</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>15.5%</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>+520</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>16.1%</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>+521</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>+520</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>nan%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>+521</t>
+          <t>+522</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>+545</t>
+          <t>+547</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4315,47 +4315,47 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>+522</t>
+          <t>+525</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>+531</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>+520</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
           <t>16.1%</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>+547</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>15.5%</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>+520</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>+500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>+525</t>
+          <t>+526</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>+531</t>
+          <t>+532</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4456,27 +4456,27 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>+526</t>
+          <t>+527</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>+532</t>
+          <t>+565</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4491,39 +4491,39 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+500</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>+527</t>
+          <t>+532</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>+565</t>
+          <t>+545</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4538,24 +4538,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>+500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Wilyer Abreu</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>+532</t>
+          <t>+533</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4565,44 +4565,44 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>+545</t>
+          <t>+535</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+520</t>
+          <t>+540</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+525</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Wilyer Abreu</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>+533</t>
+          <t>+534</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>+535</t>
+          <t>+538</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4644,29 +4644,29 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
+          <t>+537</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>+534</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>15.8%</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>+538</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>15.7%</t>
-        </is>
-      </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
           <t>+540</t>
@@ -4679,19 +4679,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>+525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Christian Encarnacion-Strand</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4706,86 +4706,86 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>+534</t>
+          <t>+556</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
+          <t>+520</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>George Springer</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>+538</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>+548</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>+540</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>15.6%</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Christian Encarnacion-Strand</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>+537</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>15.7%</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>+556</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>+520</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>nan%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>+525</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>+548</t>
+          <t>+536</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4820,39 +4820,39 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>+525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>+536</t>
+          <t>+539</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5018,47 +5018,47 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Moises Ballesteros</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>+548</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Austin Wells</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>+547</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>15.4%</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>+557</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>+555</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>15.3%</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>+540</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>15.6%</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
@@ -5067,12 +5067,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Moises Ballesteros</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>+549</t>
+          <t>+548</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>+559</t>
+          <t>+557</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>+550</t>
+          <t>+549</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>+560</t>
+          <t>+559</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5913,27 +5913,27 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>+598</t>
+          <t>+591</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+593</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5948,24 +5948,24 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+598</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5995,19 +5995,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+575</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6022,22 +6022,22 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+610</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>+601</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6069,22 +6069,22 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>+593</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>+604</t>
+          <t>+607</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>+630</t>
+          <t>+610</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -6136,59 +6136,59 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>+575</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>Yohandy Morales</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>+607</t>
+          <t>+609</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+630</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>+610</t>
+          <t>+590</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
@@ -6289,47 +6289,47 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Yohandy Morales</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>+609</t>
+          <t>+613</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>+630</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>13.7%</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>+610</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
           <t>14.1%</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>+630</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>+590</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>14.5%</t>
-        </is>
-      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -6947,12 +6947,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>+689</t>
+          <t>+690</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -6962,22 +6962,22 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>+670</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+680</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -6994,27 +6994,27 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+695</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>+710</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>+695</t>
+          <t>+696</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7056,59 +7056,59 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
+          <t>+680</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
           <t>+710</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>12.3%</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>+680</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>12.8%</t>
-        </is>
-      </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Enrique Hernandez</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>+696</t>
+          <t>+703</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>+680</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>+703</t>
+          <t>+705</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -7276,47 +7276,47 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>+705</t>
+          <t>+715</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>+710</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>+700</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Ben Ross</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Ben Ross</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7840,37 +7840,37 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>+745</t>
+          <t>+740</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
+          <t>+720</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>12.2%</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
           <t>+760</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>11.6%</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>+730</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>12.0%</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -7887,12 +7887,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+745</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7902,22 +7902,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -7934,84 +7934,84 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Alejandro Kirk</t>
+          <t>Pavin Smith</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>+753</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+730</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>+759</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8028,54 +8028,54 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Michael Gasper</t>
+          <t>Alejandro Kirk</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
+          <t>+753</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>11.7%</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
           <t>+760</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>11.6%</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>+760</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>11.6%</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Michael Gasper</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8169,37 +8169,37 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
+          <t>+765</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>11.6%</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
           <t>+770</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>11.5%</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>+790</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>11.2%</t>
-        </is>
-      </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8216,37 +8216,37 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>+775</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+750</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+775</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8278,22 +8278,22 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>+760</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Mark Vientos</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8404,37 +8404,37 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Mark Vientos</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>+785</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>+780</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+760</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8451,7 +8451,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>+788</t>
+          <t>+785</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+780</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -8533,39 +8533,39 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>+775</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>+791</t>
+          <t>+788</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>+810</t>
+          <t>+800</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -8592,12 +8592,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>+794</t>
+          <t>+791</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8607,44 +8607,44 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>+770</t>
+          <t>+810</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+775</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>+795</t>
+          <t>+794</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8654,22 +8654,22 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+770</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -8686,7 +8686,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Pavin Smith</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>+803</t>
+          <t>+801</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8748,69 +8748,69 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
+          <t>+840</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>10.6%</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
           <t>+790</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>11.2%</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>+820</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>10.9%</t>
-        </is>
-      </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+775</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>+809</t>
+          <t>+803</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9015,12 +9015,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>+819</t>
+          <t>+818</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -9050,19 +9050,19 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+775</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+819</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -9124,22 +9124,22 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>+790</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9156,27 +9156,27 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Graham Pauley</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>+825</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>+830</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -9203,12 +9203,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Graham Pauley</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>+827</t>
+          <t>+825</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -9218,32 +9218,32 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>+790</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9391,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+844</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -9438,37 +9438,37 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>+844</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>+820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9485,12 +9485,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+854</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9500,22 +9500,22 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+820</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Thomas Saggese</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -9579,27 +9579,27 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+854</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+830</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -9626,7 +9626,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -9641,22 +9641,22 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>+850</t>
+          <t>+840</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>+865</t>
+          <t>+860</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>+870</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -9767,27 +9767,27 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>+870</t>
+          <t>+865</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>+860</t>
+          <t>+850</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -9861,47 +9861,47 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
+          <t>+877</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>+880</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
           <t>+875</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr">
         <is>
           <t>10.3%</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>+870</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>10.3%</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>+880</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>10.2%</t>
-        </is>
-      </c>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr">
-        <is>
-          <t>nan%</t>
         </is>
       </c>
     </row>
@@ -9955,12 +9955,12 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>T.J. Rumfield</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>+877</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9970,91 +9970,91 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+880</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>+880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>+875</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>T.J. Rumfield</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
+          <t>+882</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>+890</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
           <t>+880</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>10.2%</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>+880</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>10.2%</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+875</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>+882</t>
+          <t>+885</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -10084,19 +10084,19 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>+875</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -10143,59 +10143,59 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>+885</t>
+          <t>+888</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>+910</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>+880</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
           <t>10.2%</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t>+890</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>10.1%</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>+880</t>
-        </is>
-      </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>10.2%</t>
-        </is>
-      </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+875</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>+888</t>
+          <t>+890</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>+910</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -10225,19 +10225,19 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>+875</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Josue De Paula</t>
+          <t>Maikel Garcia</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Maikel Garcia</t>
+          <t>Josue De Paula</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -10863,22 +10863,22 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+930</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -10895,12 +10895,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+932</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10910,32 +10910,32 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>+930</t>
+          <t>+980</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+900</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -11036,27 +11036,27 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>+938</t>
+          <t>+935</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+950</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -11071,24 +11071,24 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>+900</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>+939</t>
+          <t>+938</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -11098,22 +11098,22 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>+940</t>
+          <t>+1000</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>+980</t>
+          <t>+920</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11271,37 +11271,37 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>+966</t>
+          <t>+973</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
+          <t>+940</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>9.6%</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
           <t>+980</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>9.3%</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>+920</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>9.8%</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11694,7 +11694,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -11788,7 +11788,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -12399,27 +12399,27 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Brett Bateman</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>+1113</t>
+          <t>+1107</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>+1120</t>
+          <t>+1100</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -12446,7 +12446,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Brett Bateman</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -12681,27 +12681,27 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>+1190</t>
+          <t>+1169</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>+1180</t>
+          <t>+1140</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -12728,59 +12728,59 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
+          <t>+1190</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>7.8%</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>+1180</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>7.8%</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
           <t>+1200</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr">
         <is>
           <t>7.7%</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
-        <is>
-          <t>+1200</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="F262" s="2" t="inlineStr">
-        <is>
-          <t>+1200</t>
-        </is>
-      </c>
-      <c r="G262" s="2" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Scott Bandura</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>+1207</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -12822,54 +12822,54 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Scott Bandura</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>+1208</t>
+          <t>+1207</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>+1220</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
           <t>7.6%</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>+1160</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>+1260</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1200</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Samad Taylor</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -13198,7 +13198,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Samad Taylor</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -13668,27 +13668,27 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>+2052</t>
+          <t>+2109</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>+1640</t>
+          <t>+1820</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
@@ -13703,24 +13703,24 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>+2200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>+2109</t>
+          <t>+2132</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>+1820</t>
+          <t>+1640</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2500</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
